--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$109</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4078" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="622">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}sba-1:Details (GdB, Merkzeichen, Gültigkeitszeitraum) nur zulässig, wenn ein Schwerbehindertenausweis vorliegt (valueCodeableConcept = ja/Code 1). {component.exists() implies value.ofType(CodeableConcept).coding.where(system = 'http://terminology.hl7.org/CodeSystem/v2-0136' and code = 'Y').exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}sba-1:Details (GdB, Merkzeichen, Gültigkeitszeitraum) nur zulässig, wenn ein Schwerbehindertenausweis vorliegt (valueCodeableConcept = ja/Code 1). {component.exists() implies value.ofType(CodeableConcept).coding.where(system = 'http://terminology.hl7.org/CodeSystem/v2-0532' and code = 'Y').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -875,6 +875,66 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="101720-1"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -2244,7 +2304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP105"/>
+  <dimension ref="A1:AP109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.4921875" customWidth="true" bestFit="true"/>
@@ -5306,7 +5366,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>259</v>
       </c>
@@ -5325,7 +5385,7 @@
         <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -5428,7 +5488,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>273</v>
       </c>
@@ -5441,35 +5501,31 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5517,7 +5573,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5529,22 +5585,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5552,14 +5608,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5575,19 +5631,19 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>284</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>116</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>117</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5625,19 +5681,19 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>121</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5649,7 +5705,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5658,38 +5714,38 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5698,19 +5754,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>291</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5720,7 +5776,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5759,13 +5815,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5774,44 +5830,44 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5820,19 +5876,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5881,7 +5937,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5896,30 +5952,30 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5927,13 +5983,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5942,18 +5998,20 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6001,7 +6059,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6016,19 +6074,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6036,10 +6094,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6062,18 +6120,18 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6121,7 +6179,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6136,19 +6194,19 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>324</v>
+        <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6156,14 +6214,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6182,19 +6240,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6231,17 +6289,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6250,52 +6310,50 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6304,19 +6362,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>243</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6341,11 +6399,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6363,7 +6423,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6372,36 +6432,36 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6415,29 +6475,27 @@
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6461,13 +6519,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6485,7 +6543,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6494,7 +6552,7 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6506,13 +6564,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>192</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6520,14 +6578,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6543,22 +6601,20 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6583,13 +6639,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6607,7 +6663,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6622,30 +6678,30 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6656,7 +6712,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6665,22 +6721,22 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6717,28 +6773,26 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6747,29 +6801,31 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6787,21 +6843,23 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6825,13 +6883,11 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6849,7 +6905,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6858,7 +6914,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6867,27 +6923,27 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>381</v>
+        <v>357</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6901,7 +6957,7 @@
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6913,16 +6969,16 @@
         <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6947,13 +7003,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6971,7 +7027,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6980,7 +7036,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6992,10 +7048,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>389</v>
+        <v>192</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7006,21 +7062,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7032,18 +7088,20 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>392</v>
+        <v>243</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7067,13 +7125,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7091,13 +7149,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -7109,27 +7167,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7140,7 +7198,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7152,18 +7210,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7211,13 +7271,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -7229,27 +7289,27 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7260,7 +7320,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7272,20 +7332,18 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>410</v>
+        <v>243</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7309,13 +7367,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7333,45 +7391,45 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>415</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7394,16 +7452,20 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>402</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7427,13 +7489,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7451,7 +7513,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7463,7 +7525,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7472,10 +7534,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>409</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7486,21 +7548,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7512,16 +7574,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>411</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
+        <v>413</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>117</v>
+        <v>414</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7571,81 +7633,79 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>111</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>420</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>199</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7693,45 +7753,45 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>192</v>
+        <v>426</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7742,7 +7802,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7754,16 +7814,20 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7811,19 +7875,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>434</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7832,10 +7896,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7846,10 +7910,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7872,13 +7936,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>426</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>109</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7929,7 +7993,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>432</v>
+        <v>110</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7938,10 +8002,10 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7950,10 +8014,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>435</v>
+        <v>111</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7964,21 +8028,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7990,20 +8054,18 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>115</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8027,13 +8089,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8051,31 +8113,31 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>121</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>362</v>
+        <v>111</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8086,14 +8148,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8106,25 +8168,25 @@
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>448</v>
+        <v>117</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>449</v>
+        <v>199</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8149,13 +8211,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8173,7 +8235,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8185,19 +8247,19 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8208,10 +8270,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8234,18 +8296,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>456</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8293,7 +8353,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8302,7 +8362,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8314,10 +8374,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8328,10 +8388,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8354,13 +8414,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>445</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8411,7 +8471,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8420,7 +8480,7 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8432,10 +8492,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8446,10 +8506,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8460,7 +8520,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8469,21 +8529,23 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>463</v>
+        <v>243</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8507,13 +8569,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8531,13 +8593,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8549,13 +8611,13 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>468</v>
+        <v>381</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8566,10 +8628,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8589,21 +8651,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>470</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8627,13 +8691,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8651,7 +8715,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8669,13 +8733,13 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>474</v>
+        <v>381</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8686,10 +8750,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8700,7 +8764,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8709,22 +8773,20 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>410</v>
+        <v>472</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8761,23 +8823,25 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AC54" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8792,10 +8856,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8806,10 +8870,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8835,10 +8899,10 @@
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>108</v>
+        <v>478</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>109</v>
+        <v>479</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8889,7 +8953,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>110</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8901,7 +8965,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8910,10 +8974,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>111</v>
+        <v>480</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8924,21 +8988,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8947,19 +9011,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>114</v>
+        <v>482</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>115</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>116</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>117</v>
+        <v>485</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9009,7 +9073,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>121</v>
+        <v>481</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9021,7 +9085,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9030,10 +9094,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>111</v>
+        <v>487</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9044,14 +9108,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9064,26 +9128,24 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>114</v>
+        <v>489</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
+        <v>491</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9131,7 +9193,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9143,7 +9205,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9152,10 +9214,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>192</v>
+        <v>493</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9166,10 +9228,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9177,10 +9239,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9192,19 +9254,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>243</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>264</v>
+        <v>498</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9229,37 +9291,35 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9271,16 +9331,16 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>269</v>
+        <v>501</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>270</v>
+        <v>502</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9288,10 +9348,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9311,23 +9371,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>493</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>494</v>
+        <v>108</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9375,7 +9431,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9387,44 +9443,44 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9436,20 +9492,18 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>498</v>
+        <v>115</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>499</v>
+        <v>116</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9473,13 +9527,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9497,19 +9551,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>497</v>
+        <v>121</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9518,10 +9572,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>351</v>
+        <v>111</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9532,14 +9586,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>353</v>
+        <v>440</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9552,25 +9606,25 @@
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>356</v>
+        <v>117</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>357</v>
+        <v>199</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9595,13 +9649,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9619,7 +9673,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>501</v>
+        <v>443</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9631,33 +9685,33 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9665,10 +9719,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9677,22 +9731,22 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>414</v>
+        <v>264</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9717,13 +9771,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9741,13 +9795,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9759,31 +9813,29 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>416</v>
+        <v>269</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9795,7 +9847,7 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
@@ -9804,19 +9856,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>410</v>
+        <v>512</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>477</v>
+        <v>349</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>479</v>
+        <v>351</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9865,13 +9917,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9883,27 +9935,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>482</v>
+        <v>355</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>483</v>
+        <v>356</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9926,16 +9978,20 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>108</v>
+        <v>517</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9959,13 +10015,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9983,7 +10039,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>110</v>
+        <v>516</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9992,10 +10048,10 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10004,10 +10060,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>111</v>
+        <v>370</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10018,14 +10074,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>113</v>
+        <v>372</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10044,18 +10100,20 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>115</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>116</v>
+        <v>374</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10079,13 +10137,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10103,7 +10161,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>121</v>
+        <v>520</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10115,37 +10173,37 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>111</v>
+        <v>381</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10158,25 +10216,25 @@
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>117</v>
+        <v>432</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>199</v>
+        <v>433</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10225,7 +10283,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>424</v>
+        <v>521</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10237,7 +10295,7 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10246,10 +10304,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>192</v>
+        <v>436</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10258,26 +10316,28 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
@@ -10286,19 +10346,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>243</v>
+        <v>429</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>264</v>
+        <v>498</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10308,7 +10368,7 @@
         <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>82</v>
@@ -10323,13 +10383,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10347,13 +10407,13 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
@@ -10365,27 +10425,27 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>269</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>270</v>
+        <v>502</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10393,35 +10453,31 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>513</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10469,7 +10525,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10481,44 +10537,44 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10530,15 +10586,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10587,19 +10645,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10622,14 +10680,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>113</v>
+        <v>440</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10642,24 +10700,26 @@
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>115</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>116</v>
+        <v>442</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10695,19 +10755,19 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>121</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10731,7 +10791,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10742,10 +10802,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10753,7 +10813,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>93</v>
@@ -10768,19 +10828,19 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>521</v>
+        <v>243</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>525</v>
+        <v>264</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10790,7 +10850,7 @@
         <v>82</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>82</v>
@@ -10805,13 +10865,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10829,10 +10889,10 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>93</v>
@@ -10847,27 +10907,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>527</v>
+        <v>269</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>528</v>
+        <v>270</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10875,39 +10935,39 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>169</v>
+        <v>532</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>533</v>
+        <v>351</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q72" t="s" s="2">
-        <v>534</v>
-      </c>
+      <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10927,13 +10987,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10951,7 +11011,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10969,27 +11029,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>538</v>
+        <v>355</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>539</v>
+        <v>356</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11009,21 +11069,19 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>542</v>
+        <v>108</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>543</v>
+        <v>109</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>544</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11032,7 +11090,7 @@
         <v>82</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>82</v>
@@ -11071,7 +11129,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>546</v>
+        <v>110</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11083,7 +11141,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11092,10 +11150,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>548</v>
+        <v>111</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11106,21 +11164,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11129,21 +11187,21 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>551</v>
+        <v>115</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11152,7 +11210,7 @@
         <v>82</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>82</v>
@@ -11179,31 +11237,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>121</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11212,10 +11270,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>557</v>
+        <v>111</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11226,10 +11284,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11252,19 +11310,19 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>169</v>
+        <v>540</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11313,7 +11371,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11334,10 +11392,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11348,10 +11406,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>549</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11368,30 +11426,30 @@
         <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>550</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>347</v>
+        <v>552</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q76" s="2"/>
+      <c r="Q76" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="R76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11411,13 +11469,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>348</v>
+        <v>554</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>349</v>
+        <v>555</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11435,7 +11493,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>497</v>
+        <v>556</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11444,7 +11502,7 @@
         <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11456,10 +11514,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>192</v>
+        <v>557</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>351</v>
+        <v>558</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11470,21 +11528,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>501</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11493,22 +11551,20 @@
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>243</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>354</v>
+        <v>561</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>357</v>
+        <v>563</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11518,7 +11574,7 @@
         <v>82</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>82</v>
@@ -11533,13 +11589,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11557,13 +11613,13 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>501</v>
+        <v>565</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
@@ -11575,19 +11631,19 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>361</v>
+        <v>566</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>362</v>
+        <v>567</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -11595,7 +11651,7 @@
         <v>568</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>502</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11606,7 +11662,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11615,22 +11671,20 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>414</v>
+        <v>572</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11640,7 +11694,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11679,16 +11733,16 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>502</v>
+        <v>574</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>105</v>
@@ -11700,10 +11754,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>416</v>
+        <v>566</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>417</v>
+        <v>576</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11712,16 +11766,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11730,10 +11782,10 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>82</v>
@@ -11742,19 +11794,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>410</v>
+        <v>169</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>476</v>
+        <v>579</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>477</v>
+        <v>580</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>478</v>
+        <v>581</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>479</v>
+        <v>582</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11803,13 +11855,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>475</v>
+        <v>583</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11824,10 +11876,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>482</v>
+        <v>566</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>483</v>
+        <v>584</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11838,10 +11890,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11864,16 +11916,20 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>108</v>
+        <v>517</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11897,13 +11953,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11921,7 +11977,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>110</v>
+        <v>516</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11930,10 +11986,10 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11942,10 +11998,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>111</v>
+        <v>370</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11956,14 +12012,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>113</v>
+        <v>372</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11982,18 +12038,20 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>115</v>
+        <v>373</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>116</v>
+        <v>374</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12017,13 +12075,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12041,7 +12099,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>121</v>
+        <v>520</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12053,37 +12111,37 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>111</v>
+        <v>381</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12096,25 +12154,25 @@
         <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>117</v>
+        <v>432</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>199</v>
+        <v>433</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12163,7 +12221,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>424</v>
+        <v>521</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12175,7 +12233,7 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12184,10 +12242,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>192</v>
+        <v>436</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12196,26 +12254,28 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12224,19 +12284,19 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>243</v>
+        <v>429</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>264</v>
+        <v>498</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12246,7 +12306,7 @@
         <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>82</v>
@@ -12261,13 +12321,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12285,13 +12345,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12303,16 +12363,16 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>269</v>
+        <v>501</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>270</v>
+        <v>502</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>82</v>
@@ -12320,10 +12380,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12343,23 +12403,19 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>243</v>
+        <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>494</v>
+        <v>108</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12383,11 +12439,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12405,7 +12463,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12417,44 +12475,44 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12466,20 +12524,18 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>498</v>
+        <v>115</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>499</v>
+        <v>116</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12503,13 +12559,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12527,19 +12583,19 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>497</v>
+        <v>121</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12548,10 +12604,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>351</v>
+        <v>111</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12562,14 +12618,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>353</v>
+        <v>440</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12582,25 +12638,25 @@
         <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>356</v>
+        <v>117</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>357</v>
+        <v>199</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12625,13 +12681,13 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -12649,7 +12705,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>501</v>
+        <v>443</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12661,33 +12717,33 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12695,10 +12751,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12707,22 +12763,22 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>414</v>
+        <v>264</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12732,7 +12788,7 @@
         <v>82</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>82</v>
@@ -12747,13 +12803,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12771,13 +12827,13 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
@@ -12789,31 +12845,29 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>416</v>
+        <v>269</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12825,7 +12879,7 @@
         <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
@@ -12834,19 +12888,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>410</v>
+        <v>243</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>477</v>
+        <v>349</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>479</v>
+        <v>351</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12871,13 +12925,11 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12895,13 +12947,13 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
@@ -12913,27 +12965,27 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>482</v>
+        <v>355</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>483</v>
+        <v>356</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12956,16 +13008,20 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>108</v>
+        <v>517</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12989,13 +13045,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13013,7 +13069,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>110</v>
+        <v>516</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13022,10 +13078,10 @@
         <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13034,10 +13090,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>111</v>
+        <v>370</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13048,14 +13104,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>113</v>
+        <v>372</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13074,18 +13130,20 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>115</v>
+        <v>373</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>116</v>
+        <v>374</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13109,13 +13167,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13133,7 +13191,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>121</v>
+        <v>520</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13145,37 +13203,37 @@
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>111</v>
+        <v>381</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13188,25 +13246,25 @@
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>117</v>
+        <v>432</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>199</v>
+        <v>433</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13255,7 +13313,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>424</v>
+        <v>521</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13267,7 +13325,7 @@
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13276,10 +13334,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>192</v>
+        <v>436</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13288,26 +13346,28 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
@@ -13316,19 +13376,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>243</v>
+        <v>429</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>264</v>
+        <v>498</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13338,7 +13398,7 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>82</v>
@@ -13353,13 +13413,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13377,13 +13437,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13395,16 +13455,16 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>269</v>
+        <v>501</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>270</v>
+        <v>502</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
@@ -13412,10 +13472,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13435,23 +13495,19 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>494</v>
+        <v>108</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13499,7 +13555,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13511,44 +13567,44 @@
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13560,20 +13616,18 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>498</v>
+        <v>115</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>499</v>
+        <v>116</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13597,13 +13651,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13621,19 +13675,19 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>497</v>
+        <v>121</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13642,10 +13696,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>351</v>
+        <v>111</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13656,14 +13710,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>353</v>
+        <v>440</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13676,25 +13730,25 @@
         <v>82</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>356</v>
+        <v>117</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>357</v>
+        <v>199</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13719,13 +13773,13 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13743,7 +13797,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>501</v>
+        <v>443</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13755,33 +13809,33 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13789,10 +13843,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13801,22 +13855,22 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>414</v>
+        <v>264</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13826,7 +13880,7 @@
         <v>82</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>82</v>
@@ -13841,13 +13895,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13865,13 +13919,13 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
@@ -13883,31 +13937,29 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>416</v>
+        <v>269</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13919,7 +13971,7 @@
         <v>93</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -13928,19 +13980,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>410</v>
+        <v>321</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>477</v>
+        <v>349</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>479</v>
+        <v>351</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13989,13 +14041,13 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
@@ -14007,27 +14059,27 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>482</v>
+        <v>355</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>483</v>
+        <v>356</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14050,16 +14102,20 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>108</v>
+        <v>517</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14083,13 +14139,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14107,7 +14163,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>110</v>
+        <v>516</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14116,10 +14172,10 @@
         <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14128,10 +14184,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>111</v>
+        <v>370</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14142,14 +14198,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>113</v>
+        <v>372</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14168,18 +14224,20 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>115</v>
+        <v>373</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>116</v>
+        <v>374</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14203,13 +14261,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14227,7 +14285,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>121</v>
+        <v>520</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14239,37 +14297,37 @@
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>111</v>
+        <v>381</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14282,25 +14340,25 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>117</v>
+        <v>432</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>199</v>
+        <v>433</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14349,7 +14407,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>424</v>
+        <v>521</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14361,7 +14419,7 @@
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14370,10 +14428,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>192</v>
+        <v>436</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14382,26 +14440,28 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
@@ -14410,19 +14470,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>243</v>
+        <v>429</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>264</v>
+        <v>498</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14432,7 +14492,7 @@
         <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>82</v>
@@ -14447,13 +14507,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14471,13 +14531,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14489,16 +14549,16 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>269</v>
+        <v>501</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>270</v>
+        <v>502</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -14506,10 +14566,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14529,23 +14589,19 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>494</v>
+        <v>108</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14593,7 +14649,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14605,44 +14661,44 @@
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14654,20 +14710,18 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>498</v>
+        <v>115</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>499</v>
+        <v>116</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14691,13 +14745,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14715,19 +14769,19 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>497</v>
+        <v>121</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14736,10 +14790,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>351</v>
+        <v>111</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14750,14 +14804,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>353</v>
+        <v>440</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14770,25 +14824,25 @@
         <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>356</v>
+        <v>117</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>357</v>
+        <v>199</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14813,13 +14867,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14837,7 +14891,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>501</v>
+        <v>443</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14849,33 +14903,33 @@
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14883,10 +14937,10 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14895,22 +14949,22 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>414</v>
+        <v>264</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14920,7 +14974,7 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>82</v>
@@ -14935,13 +14989,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14959,13 +15013,13 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
@@ -14977,23 +15031,511 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>416</v>
+        <v>269</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP105">
+  <autoFilter ref="A1:AP109">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15003,7 +15545,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI108">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
+++ b/StructureDefinition-mii-pr-sdd-schwerbehindertenausweis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
